--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Tactics.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Tactics.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Feiticeiro</t>
+          <t>Malditor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ladino</t>
+          <t>Trapaceiro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -894,6 +894,33 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>コクーン</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>runner</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EA 23.299</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Corredor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Runner</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ランナー</t>
         </is>
       </c>
     </row>
